--- a/组合实盘追踪/20260611_银河.xlsx
+++ b/组合实盘追踪/20260611_银河.xlsx
@@ -574,7 +574,7 @@
         <v>-53.9</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0229</v>
+        <v>0.023</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -657,7 +657,7 @@
         <v>-54.9</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0281</v>
+        <v>0.0283</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -740,7 +740,7 @@
         <v>-68.3</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0233</v>
+        <v>0.0234</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -823,7 +823,7 @@
         <v>-41.1</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0331</v>
+        <v>0.0332</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -906,7 +906,7 @@
         <v>-123.1</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0296</v>
+        <v>0.0298</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>7.95</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1053</v>
+        <v>0.1059</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -1072,7 +1072,7 @@
         <v>-20.7</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0267</v>
+        <v>0.0268</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1155,7 +1155,7 @@
         <v>-1038.04</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6731</v>
+        <v>0.6767</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1238,7 +1238,7 @@
         <v>-5.3</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0232</v>
+        <v>0.0233</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1321,7 +1321,7 @@
         <v>-24.1</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0291</v>
+        <v>0.0293</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1404,7 +1404,7 @@
         <v>-1421.49</v>
       </c>
       <c r="Q12" s="2">
-        <v>0.9944</v>
+        <v>0.9997</v>
       </c>
       <c r="R12" t="str">
         <v/>
